--- a/tame_output/ON/bt/strategyON_20240303.xlsx
+++ b/tame_output/ON/bt/strategyON_20240303.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-72.3%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191742</v>
+        <v>3.302618194191743</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108644</v>
+        <v>3.305023265108645</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097825</v>
+        <v>3.341378723097826</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.374439043094122</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.405960511199292</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.4246333549696</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923093</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297755</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>0.8911040173364784</v>
+        <v>0.8923139863930845</v>
       </c>
       <c r="E1891" t="n">
-        <v>3.533074960970108</v>
+        <v>3.53355894859275</v>
       </c>
       <c r="F1891" t="n">
         <v>1.679858856261937</v>

--- a/tame_output/ON/bt/strategyON_20240303.xlsx
+++ b/tame_output/ON/bt/strategyON_20240303.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>516.8%</t>
+          <t>516.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-22.8%</t>
         </is>
       </c>
     </row>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>0.8923139863930845</v>
+        <v>0.893141916606606</v>
       </c>
       <c r="E1891" t="n">
-        <v>3.53355894859275</v>
+        <v>3.533890120678159</v>
       </c>
       <c r="F1891" t="n">
         <v>1.679858856261937</v>

--- a/tame_output/ON/bt/strategyON_20240303.xlsx
+++ b/tame_output/ON/bt/strategyON_20240303.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>516.9%</t>
+          <t>504.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-99.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-33.9%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191743</v>
+        <v>3.302618194191742</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108645</v>
+        <v>3.305023265108644</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097826</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199292</v>
+        <v>3.405960511199291</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>0.893141916606606</v>
+        <v>0.6171393000455087</v>
       </c>
       <c r="E1891" t="n">
-        <v>3.533890120678159</v>
+        <v>3.42348907405372</v>
       </c>
       <c r="F1891" t="n">
         <v>1.679858856261937</v>
